--- a/data/combined/processed/codebook_scalelevel.xlsx
+++ b/data/combined/processed/codebook_scalelevel.xlsx
@@ -384,7 +384,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Scale name (or attitude-object name).</t>
         </is>
       </c>
     </row>
@@ -401,7 +401,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Dataset / contributing-sample label.</t>
         </is>
       </c>
     </row>
@@ -418,7 +418,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Variable type: 'trait' or 'attitude'.</t>
         </is>
       </c>
     </row>
@@ -435,7 +435,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Cronbach's alpha (raw) for the scale; NA for single-item scales.</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Full-scale item count.</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Theoretical minimum of the item response scale.</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Theoretical maximum of the item response scale.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Number of participants contributing a sum score.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Mean sum score.</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Standard deviation of the sum score (Bessel-corrected, n-1; reportable).</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Population SD of the sum score (n denominator); used in the POMP ratios.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Observed minimum sum score.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Observed maximum sum score.</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Skewness of the sum score (psych::skew).</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Excess kurtosis of the sum score (psych::kurtosi).</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Theoretical minimum possible sum score (min_response * n_items).</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Theoretical maximum possible sum score (max_response * n_items).</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Logical sum-score range (logical_max - logical_min).</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>Local Bhatia-Davis (2000) max-SD bound given the mean: sqrt((logical_max - m)(m - logical_min)).</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>POMP mean: (m - logical_min) / max_range.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>SD / logical range (proportion of max range).</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>SD / (range/2): proportion of the global Popoviciu max SD.</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>SD / max_sd_bd: proportion of the local Bhatia-Davis (2000) max SD.</t>
         </is>
       </c>
     </row>
